--- a/data/daily/2026-10/2026-10-10.xlsx
+++ b/data/daily/2026-10/2026-10-10.xlsx
@@ -1170,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,60 +1267,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1425,107 +1425,107 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 적합 — 깔끔하고 고급스러운 패키지 구성으로 선물 시 만족도가 높음</t>
+          <t>선물용 만족도 — 패키지 구성과 디자인이 깔끔하여 생일이나 감사 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>간편한 섭취 — 물품 구성이 간편하여 피로할 때 하나씩 꺼내 먹기 편함</t>
+          <t>피로 회복 체감 — 피곤하고 지칠 때 섭취 시 활력 충전 및 피로 개선에 도움됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>피로 회복 체감 — 피곤하고 지칠 때 섭취 시 활력 충전 및 피로 개선에 도움 됨</t>
+          <t>간편한 섭취 방식 — 개별 포장되어 피곤할 때마다 간편하게 꺼내 먹기 용이함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송 처리가 너무 느려 수령까지 지루하고 답답함</t>
+          <t>배송 지연 불만 — 배송 속도가 매우 느려 답답했다는 불만이 있음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2659,21 +2659,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15565</v>
+        <v>15566</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 패키지가 고급스럽고 예뻐 생일이나 응원 선물로 적합함</t>
+          <t>섭취 편의성 및 휴대성 — 한 병씩 개별 포장되어 휴대하기 편하고 물 없이도 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>우수한 휴대·복용성 — 한 병씩 개별 포장되어 휴대가 편하고 간편하게 섭취 가능함</t>
+          <t>부담 없는 맛 — 동봉된 시럽이 달짝지근하여 비타민 알약과 함께 삼키기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>달콤한 시럽 맛 — 비타민과 함께 넘기는 액상이 달짝지근하여 거부감 없이 섭취 가능함</t>
+          <t>선물 만족도 — 패키지가 고급스럽고 예뻐 생일이나 응원 선물로 받거나 주기에 적합함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 피로 해소 — 복용 시 몸의 활력이 달라지고 다음 날 피로감이 줄어드는 느낌을 받음</t>
+          <t>피로 회복 체감 — 섭취 후 다음 날 피로가 덜하고 일상 속 활력이 돋는 체감 효과가 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진한 액상 제형 — 타사 액상 제품 대비 농도가 진하여 복용 만족도가 높음</t>
+          <t>선물용 인기 — 꼼꼼하고 고급스러운 포장으로 선물용으로 주고받기 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>꼼꼼한 포장 배송 — 포장이 꼼꼼하게 배송되어 선물용이나 자가 소비 시 만족도가 높음</t>
+          <t>진한 액상 퀄리티 — 타사 액상 비타민 대비 농도가 진하고 만족스러움</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2781,17 +2781,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 쫀득하고 새콤달콤한 젤리 제형으로 간식처럼 맛있게 섭취 가능함</t>
+          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형으로 간식처럼 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알약 대비 복용 용이 — 목넘김이 어려운 알약 대신 간편하게 씹어 먹을 수 있어 부담이 적음</t>
+          <t>복용 편의성 — 목넘김이 부담스러운 알약을 잘 삼키지 못하는 사람도 쉽게 영양 보충 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>선물 포장 만족 — 귀여운 패키지와 예쁜 선물 포장으로 선물용으로 인기가 높음</t>
+          <t>귀여운 패키지 — 손잡이가 달린 귀여운 패키지와 증정 키캡 등 선물용으로 구성이 만족스러움</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,22 +2840,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 복용 며칠 만에 눈의 피로와 오후 시간대 체력 저하 완화 체감</t>
+          <t>빠른 피로 개선 — 섭취 후 체력 저하와 눈의 피로감이 줄어들고 에너지 충전에 도움됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 휴대성 — 견고한 개별 포장으로 출근길이나 외출 시 가방에 챙겨 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>물 없는 간편 섭취 — 물 없이도 목넘김이 깔끔하고 맛이 좋아 간편하게 섭취 가능함</t>
-        </is>
-      </c>
+          <t>휴대 및 복용 편의 — 물 없이도 간편하게 섭취 가능하며 튼튼한 개별 포장으로 휴대가 용이함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>단품 배송 포장 아쉬움 — 별도 쇼핑백 없이 일반 박스에만 배송되어 선물 포장으로 다소 아쉬움</t>
+          <t>배송 포장 아쉬움 — 쇼핑백 없이 박스에 본품만 담겨 배송되어 선물 포장 상태가 다소 아쉬움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2903,24 +2899,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>간편한 복용 및 휴대 — 알약과 액상 세트 구성으로 외출 시 한 병씩 가방에 챙겨 먹기 편함</t>
+          <t>간편한 섭취와 휴대 — 알약과 액상이 세트로 구성되어 외출 시 가방에 넣고 간편히 섭취 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 섭취 후 아침 기상 시 개운함이 느껴지고 컨디션 회복에 도움 됨</t>
+          <t>선물용으로 적합 — 패키지가 깔끔하고 고급스러워 생일 선물용으로 인기가 높음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 포장이 깔끔하고 고급스러워 지인 생일 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>다소 적은 용량 구성 — 소포장 구성으로 선물 시 겉보기에 풍성한 느낌이 부족함</t>
-        </is>
-      </c>
+          <t>아침 피로 회복 — 자기 전이나 피곤할 때 섭취 후 다음 날 아침 활력 개선에 도움됨</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2962,21 +2954,21 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 명절 포장 — 고급스러운 박스와 종이가방 패키지로 명절 선물용으로 적합함</t>
+          <t>고급스러운 포장 — 박스와 종이가방이 정갈하고 예뻐 명절이나 특별한 날 선물용으로 만족스러움</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 한 병씩 구성되어 출근 시 가볍게 챙겨 먹기 수월함</t>
+          <t>부담 없는 구성 — 10일분 구성이라 부담 없이 체험하기 좋고 출근길에 가볍게 챙기기 용이함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>활력 충전 도움 — 환절기나 바쁜 일상에서 면역력 관리 및 활력 충전에 도움 됨</t>
+          <t>활력 충전 효과 — 환절기 면역 관리와 일상 속 체력 저하 완화에 도움됨</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3025,17 +3017,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>깔끔하고 독특한 포장 — 각 잡힌 깔끔한 패키지와 신기한 포장 구성으로 선물용 만족도가 높음</t>
+          <t>빠른 피로 회복 — 섭취 후 빠르게 활력이 충전되고 피로감이 줄어드는 느낌을 받음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>즉각적인 활력 회복 — 섭취 후 피로가 풀리고 활력이 더해지는 효과를 체감함</t>
+          <t>간편하고 깔끔한 포장 — 각 잡힌 패키지로 선물하기 좋으며 액상형이라 어디서나 섭취하기 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>맛있고 간편한 액상 — 맛이 거부감 없이 좋으며 액상 형태로 간편하게 섭취 가능함</t>
+          <t>부담 없는 맛 — 거부감 없는 맛있는 맛으로 간편하게 활력을 보충하기 적합함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3084,17 +3076,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤형 구성 — 남성과 여성용 비타민이 구분되어 필요에 맞게 선택 및 선물 가능함</t>
+          <t>성별 맞춤 구성 — 남성과 여성에 맞춘 영양 설계로 세분화되어 있어 만족스러움</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>쓴맛 없는 복용감 — 비타민 특유의 쓴맛이 없고 농도가 진해 거부감 없이 마시기 수월함</t>
+          <t>부담 없는 맛과 목넘김 — 비타민 특유의 쓴맛 없이 진하고 먹기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>체력 증진 도움 — 직장인 피로 회복과 활력 증진에 포션처럼 빠른 도움이 됨</t>
+          <t>활력 개선 체감 — 섭취 후 피로가 덜하고 업무나 일상에서 에너지 보충 체감이 큼</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3104,7 +3096,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3112,55 +3104,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28,000원</t>
+          <t>23,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/3252731</t>
+          <t>https://gift.kakao.com/product/7948462</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260927232309_d6a091055c604810a078748974bfb7eb.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>955</v>
+        <v>29829</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>고함량 비타민C 체감 — 피로 완화와 피부 및 컨디션 관리에 확실한 변화를 체감함</t>
+          <t>피로 개선 효과 — 아침마다 섭취 시 피로감이 줄어들고 생기와 활력이 돋는 것을 느낌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>신뢰도 높은 원료 — 영국산 비타민C 원산지로 품질에 대한 신뢰도가 높음</t>
+          <t>복용 편의성과 맛 — 액상이 맛있어 알약과 함께 넘기기 쉽고 휴대하며 챙기기 좋음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>선물용 무난함 — 호불호가 적고 누구나 섭취하기 좋아 지인 선물로 유용함</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>강한 신맛 및 복용 거부감 — 분말 특유의 신맛이 매우 강해 섭취하기 부담스럽거나 맛이 없음</t>
-        </is>
-      </c>
+          <t>높은 가성비와 브랜드 신뢰 — 합리적인 가격대에 믿을 수 있는 종근당 브랜드라 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3202,21 +3190,21 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>풍성한 굿즈 구성 — 포토카드, 엽서, 단백질바 등이 포함된 다채로운 구성으로 만족도가 높음</t>
+          <t>맛있는 효소 맛 — 특유의 쿰쿰함 없이 맛이 좋아 거부감 없이 간편히 먹기 좋음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>간편한 스틱 섭취 — 한 포씩 개별 포장되어 있어 휴대가 편리하고 복용하기 수월함</t>
+          <t>소화 및 배변 도움 — 섭취 후 더부룩함이 줄고 화장실을 잘 가게 되는 등 배변에 도움됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>부담 없는 맛 — 기존 오리지널 효소에 비해 거부감 없이 맛있게 섭취 가능함</t>
+          <t>알찬 사은품 구성 — 단백질바나 포토카드 등 함께 제공되는 구성품이 풍성하고 만족스러움</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -3265,17 +3253,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>소화 및 속 편안함 — 밀가루 섭취 후 복용 시 소화가 잘되고 속이 편안해짐</t>
+          <t>소화 편안함 체감 — 밀가루 등 식사 후 섭취 시 소화가 잘되고 속이 편안해짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수한 고구마 맛 — 특유의 거부감 없이 구수한 고구마 맛이 나서 가족 모두 섭취하기 좋음</t>
+          <t>구수한 곡물 맛 — 구수한 고구마 맛과 곡물 맛으로 거부감 없이 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>알찬 사은품 혜택 — 견과류바와 차 등 추가 증정품 구성이 알차 가성비 만족도가 높음</t>
+          <t>풍성한 사은품 증정 — 추가 증정포와 견과류바 등 사은품 혜택이 푸짐함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3324,22 +3312,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 포장 패키지 — 오간자 패키지와 플리츠백 구성으로 열었을 때 감동을 주는 선물로 적합함</t>
+          <t>고급스러운 선물 패키지 — 오간자 에디션 및 패키지 디자인이 예뻐 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>맛있는 앰플 형태 — 비린 맛 없이 맛이 좋아 하루 한 병씩 부담 없이 마시기 편함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>피로 완화 도움 — 피부 탄력 기대감과 함께 복용 후 피로감이 덜해지는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>맛있는 앰플 제형 — 비린 맛 없이 맛이 좋아 하루 한 병씩 꾸준히 챙겨 마시기 편함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 정가 기준 가격대가 높아 할인 기간에만 구매하게 됨</t>
+          <t>높은 정가 부담 — 품질은 만족스러우나 정가가 비싸 할인 행사 시에만 구매하게 됨</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3387,17 +3371,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양한 소스가 맛있음</t>
+          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 닭가슴살이 촉촉하며 부드러움</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지에 간단히 데우기만 하면 되어 식사 대용으로 편리함</t>
+          <t>다양하고 맛있는 양념 — 떡볶이맛 등 양념이 다양하고 맛있어 식단 관리가 질리지 않음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>높은 가성비 — 세일 및 할인 행사 시 저렴한 가격에 쟁여두기 좋음</t>
+          <t>간편한 조리 방식 — 전자레인지에 간단히 데워 즉시 먹을 수 있어 식사 대용으로 편리함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3446,17 +3430,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 아침 몸의 무거움과 숙취가 눈에 띄게 덜함</t>
+          <t>다음 날 숙취 완화 — 음주 전후 섭취 시 다음 날 두통이나 숙취의 무거운 느낌이 확연히 덜함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>선물용 고급 쇼핑백 — 리본 손잡이가 달린 보라색 패키지로 애주가 선물용으로 고급스러움</t>
+          <t>휴대 및 복용 용이 — 개별 스틱 포장으로 가방이나 주머니에 넣어 다니다 물 없이 바로 섭취 가능함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>간편한 스틱 액상 — 물 없이 바로 짜먹을 수 있는 작은 스틱 형태로 술자리 휴대성이 뛰어남</t>
+          <t>깔끔하고 고급스러운 포장 — 보라색 쇼핑백과 정갈한 패키지로 술자리 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3474,62 +3458,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1535</v>
+        <v>1911</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 아침 기상 시 몸이 한결 가볍고 운동 중 집중력과 체력 관리에 도움 됨</t>
+          <t>운동 수행 능력 향상 — 꾸준히 섭취 시 세트 수행 개수가 늘고 지치지 않으며 근회복에 도움됨</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>알찬 2개월분 세트 — 아르기닌과 밀크씨슬(마카) 조합을 넉넉한 2개월분으로 챙길 수 있음</t>
+          <t>우수한 풀림성 — 입자가 고와 뭉침 없이 잘 녹아 단백질 보충제나 음료에 섞기 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>신뢰도 높은 모델 조합 — 김종국 추천 영양제 세트로 브랜드 신뢰도가 높아 선물용으로 좋음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백의 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+          <t>스쿱 동봉 편의성 — 통 안에 전용 스쿱이 포함되어 있어 정량 섭취가 용이함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3537,7 +3517,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3547,38 +3527,38 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1910</v>
+        <v>1183</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>운동 수행능력 향상 — 섭취 2~3주 후 운동 시 수행 개수가 늘고 덜 지치는 효과를 체감함</t>
+          <t>맛있는 매실 맛 — 거부감 없는 맛있는 매실 향과 맛으로 물 대신 시원하게 마시기 좋음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>우수한 풀림성과 섭취감 — 입자가 뭉침 없이 잘 녹아 단백질 보충제나 음료에 섞어 마시기 편함</t>
+          <t>뛰어난 가루 풀림 — 가루가 물에 쉽게 풀려 운동 전후 흔들어 마시기 간편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>스쿱 내장 편의성 — 통 안에 전용 스쿱이 동봉되어 정량 섭취 및 복용이 용이함</t>
+          <t>운동 피로 회복 체감 — 수분 및 전해질이 보충되어 운동 중 퍼포먼스 향상에 도움됨</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3588,7 +3568,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3596,51 +3576,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13586002</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007104254_bd7666cf9044472bb3ec327d17c35b29.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>1535</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>상큼 달콤한 맛 — 생강 특유의 강한 매운맛 대신 레몬과 과일이 어우러져 마시기 편함</t>
+          <t>활력 충전 체감 — 아침에 일어날 때 몸이 한결 가볍고 운동 및 일상 피로 완화에 도움됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>몸의 온기 및 활력 증진 — 공복에 섭취해도 속 쓰림이 적고 몸이 따뜻해지며 에너지가 충전됨</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>귀여운 미니보틀 패키지 — 병 디자인이 귀여워 챙겨 마시기 좋고 특별한 선물용으로 알맞음</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>알찬 2개월분 구성 — 아르기닌과 밀크씨슬을 넉넉한 2개월 용량으로 함께 챙길 수 있어 효율적임</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>쇼핑백 불량 발생 — 선물용으로 동봉된 쇼핑백에 손잡이 끈이 누락되어 배송됨</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3655,51 +3635,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/13586002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007104254_bd7666cf9044472bb3ec327d17c35b29.png</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1179</v>
+        <v>13</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>맛있는 음용감 — 매실, 알로에, 요구르트 등 맛이 뛰어나 물 대신 맛있게 음용 가능함</t>
+          <t>상큼하고 부담 없는 맛 — 과일 성분이 블렌딩되어 독한 생강 맛 대신 상큼달콤하게 마시기 좋음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 집중 및 수분 충전 — 전해질과 아미노산 보충으로 운동 수행 능력 및 집중력 향상에 도움 됨</t>
+          <t>아침 활력 충전 — 출근길 공복에 섭취 시 몸이 따뜻해지고 졸음이 깨며 활력이 돋음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>찬물 풀림성 우수 — 가루가 물에 쉽게 잘 풀려 운동 중 타서 마시기 편리함</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>귀여운 보틀 디자인 — 미니 보틀 패키지가 아기자기하고 귀여워 챙겨 마시기 즐거움</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>생강 맛 호불호 — 생강 특유의 찡하고 알싸한 맛으로 인해 어린이나 일부 가족에게는 불호가 있음</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3745,22 +3729,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>부드럽고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 부드러운 육질로 맛있게 단백질 보충 가능함</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 쫄깃하여 식감이 우수함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>한입 크기 편의성 — 닭가슴살볼이 한입 크기로 되어 있어 샐러드나 도시락 곁들임으로 먹기 편함</t>
+          <t>다양한 구성과 맛 — 소스통살과 볼 형태의 다양한 구성과 맛으로 질리지 않고 식단 관리 가능함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>간편한 조리법 — 전자레인지에 간단히 데워 양배추 등과 곁들여 먹기 용이함</t>
+          <t>간편한 조리 — 전자레인지로 데우기만 하면 되어 식사 대용으로 편리함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>다소 느린 배송 — 주문 후 수령까지 배송 속도가 다소 느리게 느껴짐</t>
+          <t>배송 다소 지연 — 일부 배송 속도가 느리게 느껴졌다는 후기가 있음</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3922,7 +3906,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3963,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>종근당</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4020,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4071,7 @@
         <v>16246</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15565</v>
+        <v>15566</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3400</v>
@@ -4102,7 +4086,7 @@
         <v>8747</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1753</v>
@@ -4111,7 +4095,7 @@
         <v>782</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>955</v>
+        <v>29829</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4122,72 +4106,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 적합 — 깔끔하고 고급스러운 패키지 구성으로 선물 시 만족도가 높음
-간편한 섭취 — 물품 구성이 간편하여 피로할 때 하나씩 꺼내 먹기 편함
-피로 회복 체감 — 피곤하고 지칠 때 섭취 시 활력 충전 및 피로 개선에 도움 됨</t>
+          <t>선물용 만족도 — 패키지 구성과 디자인이 깔끔하여 생일이나 감사 선물용으로 적합함
+피로 회복 체감 — 피곤하고 지칠 때 섭취 시 활력 충전 및 피로 개선에 도움됨
+간편한 섭취 방식 — 개별 포장되어 피곤할 때마다 간편하게 꺼내 먹기 용이함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 패키지가 고급스럽고 예뻐 생일이나 응원 선물로 적합함
-우수한 휴대·복용성 — 한 병씩 개별 포장되어 휴대가 편하고 간편하게 섭취 가능함
-달콤한 시럽 맛 — 비타민과 함께 넘기는 액상이 달짝지근하여 거부감 없이 섭취 가능함</t>
+          <t>섭취 편의성 및 휴대성 — 한 병씩 개별 포장되어 휴대하기 편하고 물 없이도 간편하게 섭취 가능함
+부담 없는 맛 — 동봉된 시럽이 달짝지근하여 비타민 알약과 함께 삼키기 좋음
+선물 만족도 — 패키지가 고급스럽고 예뻐 생일이나 응원 선물로 받거나 주기에 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 해소 — 복용 시 몸의 활력이 달라지고 다음 날 피로감이 줄어드는 느낌을 받음
-진한 액상 제형 — 타사 액상 제품 대비 농도가 진하여 복용 만족도가 높음
-꼼꼼한 포장 배송 — 포장이 꼼꼼하게 배송되어 선물용이나 자가 소비 시 만족도가 높음</t>
+          <t>피로 회복 체감 — 섭취 후 다음 날 피로가 덜하고 일상 속 활력이 돋는 체감 효과가 있음
+선물용 인기 — 꼼꼼하고 고급스러운 포장으로 선물용으로 주고받기 적합함
+진한 액상 퀄리티 — 타사 액상 비타민 대비 농도가 진하고 만족스러움</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 쫀득하고 새콤달콤한 젤리 제형으로 간식처럼 맛있게 섭취 가능함
-알약 대비 복용 용이 — 목넘김이 어려운 알약 대신 간편하게 씹어 먹을 수 있어 부담이 적음
-선물 포장 만족 — 귀여운 패키지와 예쁜 선물 포장으로 선물용으로 인기가 높음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형으로 간식처럼 거부감 없이 섭취 가능함
+복용 편의성 — 목넘김이 부담스러운 알약을 잘 삼키지 못하는 사람도 쉽게 영양 보충 가능함
+귀여운 패키지 — 손잡이가 달린 귀여운 패키지와 증정 키캡 등 선물용으로 구성이 만족스러움</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 복용 며칠 만에 눈의 피로와 오후 시간대 체력 저하 완화 체감
-간편한 휴대성 — 견고한 개별 포장으로 출근길이나 외출 시 가방에 챙겨 다니기 용이함
-물 없는 간편 섭취 — 물 없이도 목넘김이 깔끔하고 맛이 좋아 간편하게 섭취 가능함</t>
+          <t>빠른 피로 개선 — 섭취 후 체력 저하와 눈의 피로감이 줄어들고 에너지 충전에 도움됨
+휴대 및 복용 편의 — 물 없이도 간편하게 섭취 가능하며 튼튼한 개별 포장으로 휴대가 용이함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복용 및 휴대 — 알약과 액상 세트 구성으로 외출 시 한 병씩 가방에 챙겨 먹기 편함
-피로 회복 도움 — 섭취 후 아침 기상 시 개운함이 느껴지고 컨디션 회복에 도움 됨
-고급스러운 포장 — 포장이 깔끔하고 고급스러워 지인 생일 선물용으로 적합함</t>
+          <t>간편한 섭취와 휴대 — 알약과 액상이 세트로 구성되어 외출 시 가방에 넣고 간편히 섭취 가능함
+선물용으로 적합 — 패키지가 깔끔하고 고급스러워 생일 선물용으로 인기가 높음
+아침 피로 회복 — 자기 전이나 피곤할 때 섭취 후 다음 날 아침 활력 개선에 도움됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 명절 포장 — 고급스러운 박스와 종이가방 패키지로 명절 선물용으로 적합함
-간편한 개별 포장 — 한 병씩 구성되어 출근 시 가볍게 챙겨 먹기 수월함
-활력 충전 도움 — 환절기나 바쁜 일상에서 면역력 관리 및 활력 충전에 도움 됨</t>
+          <t>고급스러운 포장 — 박스와 종이가방이 정갈하고 예뻐 명절이나 특별한 날 선물용으로 만족스러움
+부담 없는 구성 — 10일분 구성이라 부담 없이 체험하기 좋고 출근길에 가볍게 챙기기 용이함
+활력 충전 효과 — 환절기 면역 관리와 일상 속 체력 저하 완화에 도움됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>깔끔하고 독특한 포장 — 각 잡힌 깔끔한 패키지와 신기한 포장 구성으로 선물용 만족도가 높음
-즉각적인 활력 회복 — 섭취 후 피로가 풀리고 활력이 더해지는 효과를 체감함
-맛있고 간편한 액상 — 맛이 거부감 없이 좋으며 액상 형태로 간편하게 섭취 가능함</t>
+          <t>빠른 피로 회복 — 섭취 후 빠르게 활력이 충전되고 피로감이 줄어드는 느낌을 받음
+간편하고 깔끔한 포장 — 각 잡힌 패키지로 선물하기 좋으며 액상형이라 어디서나 섭취하기 편함
+부담 없는 맛 — 거부감 없는 맛있는 맛으로 간편하게 활력을 보충하기 적합함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 구성 — 남성과 여성용 비타민이 구분되어 필요에 맞게 선택 및 선물 가능함
-쓴맛 없는 복용감 — 비타민 특유의 쓴맛이 없고 농도가 진해 거부감 없이 마시기 수월함
-체력 증진 도움 — 직장인 피로 회복과 활력 증진에 포션처럼 빠른 도움이 됨</t>
+          <t>성별 맞춤 구성 — 남성과 여성에 맞춘 영양 설계로 세분화되어 있어 만족스러움
+부담 없는 맛과 목넘김 — 비타민 특유의 쓴맛 없이 진하고 먹기 편함
+활력 개선 체감 — 섭취 후 피로가 덜하고 업무나 일상에서 에너지 보충 체감이 큼</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 체감 — 피로 완화와 피부 및 컨디션 관리에 확실한 변화를 체감함
-신뢰도 높은 원료 — 영국산 비타민C 원산지로 품질에 대한 신뢰도가 높음
-선물용 무난함 — 호불호가 적고 누구나 섭취하기 좋아 지인 선물로 유용함</t>
+          <t>피로 개선 효과 — 아침마다 섭취 시 피로감이 줄어들고 생기와 활력이 돋는 것을 느낌
+복용 편의성과 맛 — 액상이 맛있어 알약과 함께 넘기기 쉽고 휴대하며 챙기기 좋음
+높은 가성비와 브랜드 신뢰 — 합리적인 가격대에 믿을 수 있는 종근당 브랜드라 만족도가 높음</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4182,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송 처리가 너무 느려 수령까지 지루하고 답답함</t>
+          <t>배송 지연 불만 — 배송 속도가 매우 느려 답답했다는 불만이 있음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -4207,22 +4190,14 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>단품 배송 포장 아쉬움 — 별도 쇼핑백 없이 일반 박스에만 배송되어 선물 포장으로 다소 아쉬움</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>다소 적은 용량 구성 — 소포장 구성으로 선물 시 겉보기에 풍성한 느낌이 부족함</t>
-        </is>
-      </c>
+          <t>배송 포장 아쉬움 — 쇼핑백 없이 박스에 본품만 담겨 배송되어 선물 포장 상태가 다소 아쉬움</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛 및 복용 거부감 — 분말 특유의 신맛이 매우 강해 섭취하기 부담스럽거나 맛이 없음</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4277,7 +4252,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>28,000원</t>
+          <t>23,800원</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4425,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4502,22 +4477,22 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>타이거모닝</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4559,22 +4534,22 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4627,7 +4602,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1693</v>
@@ -4642,16 +4617,16 @@
         <v>21</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>1911</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1183</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>1535</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>13</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>1179</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>69</v>
@@ -4665,72 +4640,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>풍성한 굿즈 구성 — 포토카드, 엽서, 단백질바 등이 포함된 다채로운 구성으로 만족도가 높음
-간편한 스틱 섭취 — 한 포씩 개별 포장되어 있어 휴대가 편리하고 복용하기 수월함
-부담 없는 맛 — 기존 오리지널 효소에 비해 거부감 없이 맛있게 섭취 가능함</t>
+          <t>맛있는 효소 맛 — 특유의 쿰쿰함 없이 맛이 좋아 거부감 없이 간편히 먹기 좋음
+소화 및 배변 도움 — 섭취 후 더부룩함이 줄고 화장실을 잘 가게 되는 등 배변에 도움됨
+알찬 사은품 구성 — 단백질바나 포토카드 등 함께 제공되는 구성품이 풍성하고 만족스러움</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>소화 및 속 편안함 — 밀가루 섭취 후 복용 시 소화가 잘되고 속이 편안해짐
-구수한 고구마 맛 — 특유의 거부감 없이 구수한 고구마 맛이 나서 가족 모두 섭취하기 좋음
-알찬 사은품 혜택 — 견과류바와 차 등 추가 증정품 구성이 알차 가성비 만족도가 높음</t>
+          <t>소화 편안함 체감 — 밀가루 등 식사 후 섭취 시 소화가 잘되고 속이 편안해짐
+구수한 곡물 맛 — 구수한 고구마 맛과 곡물 맛으로 거부감 없이 맛있게 섭취 가능함
+풍성한 사은품 증정 — 추가 증정포와 견과류바 등 사은품 혜택이 푸짐함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 패키지 — 오간자 패키지와 플리츠백 구성으로 열었을 때 감동을 주는 선물로 적합함
-맛있는 앰플 형태 — 비린 맛 없이 맛이 좋아 하루 한 병씩 부담 없이 마시기 편함
-피로 완화 도움 — 피부 탄력 기대감과 함께 복용 후 피로감이 덜해지는 느낌을 받음</t>
+          <t>고급스러운 선물 패키지 — 오간자 에디션 및 패키지 디자인이 예뻐 받는 사람의 만족도가 높음
+맛있는 앰플 제형 — 비린 맛 없이 맛이 좋아 하루 한 병씩 꾸준히 챙겨 마시기 편함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양한 소스가 맛있음
-간편한 전자레인지 조리 — 전자레인지에 간단히 데우기만 하면 되어 식사 대용으로 편리함
-높은 가성비 — 세일 및 할인 행사 시 저렴한 가격에 쟁여두기 좋음</t>
+          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 닭가슴살이 촉촉하며 부드러움
+다양하고 맛있는 양념 — 떡볶이맛 등 양념이 다양하고 맛있어 식단 관리가 질리지 않음
+간편한 조리 방식 — 전자레인지에 간단히 데워 즉시 먹을 수 있어 식사 대용으로 편리함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 아침 몸의 무거움과 숙취가 눈에 띄게 덜함
-선물용 고급 쇼핑백 — 리본 손잡이가 달린 보라색 패키지로 애주가 선물용으로 고급스러움
-간편한 스틱 액상 — 물 없이 바로 짜먹을 수 있는 작은 스틱 형태로 술자리 휴대성이 뛰어남</t>
+          <t>다음 날 숙취 완화 — 음주 전후 섭취 시 다음 날 두통이나 숙취의 무거운 느낌이 확연히 덜함
+휴대 및 복용 용이 — 개별 스틱 포장으로 가방이나 주머니에 넣어 다니다 물 없이 바로 섭취 가능함
+깔끔하고 고급스러운 포장 — 보라색 쇼핑백과 정갈한 패키지로 술자리 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 아침 기상 시 몸이 한결 가볍고 운동 중 집중력과 체력 관리에 도움 됨
-알찬 2개월분 세트 — 아르기닌과 밀크씨슬(마카) 조합을 넉넉한 2개월분으로 챙길 수 있음
-신뢰도 높은 모델 조합 — 김종국 추천 영양제 세트로 브랜드 신뢰도가 높아 선물용으로 좋음</t>
+          <t>운동 수행 능력 향상 — 꾸준히 섭취 시 세트 수행 개수가 늘고 지치지 않으며 근회복에 도움됨
+우수한 풀림성 — 입자가 고와 뭉침 없이 잘 녹아 단백질 보충제나 음료에 섞기 편함
+스쿱 동봉 편의성 — 통 안에 전용 스쿱이 포함되어 있어 정량 섭취가 용이함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행능력 향상 — 섭취 2~3주 후 운동 시 수행 개수가 늘고 덜 지치는 효과를 체감함
-우수한 풀림성과 섭취감 — 입자가 뭉침 없이 잘 녹아 단백질 보충제나 음료에 섞어 마시기 편함
-스쿱 내장 편의성 — 통 안에 전용 스쿱이 동봉되어 정량 섭취 및 복용이 용이함</t>
+          <t>맛있는 매실 맛 — 거부감 없는 맛있는 매실 향과 맛으로 물 대신 시원하게 마시기 좋음
+뛰어난 가루 풀림 — 가루가 물에 쉽게 풀려 운동 전후 흔들어 마시기 간편함
+운동 피로 회복 체감 — 수분 및 전해질이 보충되어 운동 중 퍼포먼스 향상에 도움됨</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>상큼 달콤한 맛 — 생강 특유의 강한 매운맛 대신 레몬과 과일이 어우러져 마시기 편함
-몸의 온기 및 활력 증진 — 공복에 섭취해도 속 쓰림이 적고 몸이 따뜻해지며 에너지가 충전됨
-귀여운 미니보틀 패키지 — 병 디자인이 귀여워 챙겨 마시기 좋고 특별한 선물용으로 알맞음</t>
+          <t>활력 충전 체감 — 아침에 일어날 때 몸이 한결 가볍고 운동 및 일상 피로 완화에 도움됨
+알찬 2개월분 구성 — 아르기닌과 밀크씨슬을 넉넉한 2개월 용량으로 함께 챙길 수 있어 효율적임</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 음용감 — 매실, 알로에, 요구르트 등 맛이 뛰어나 물 대신 맛있게 음용 가능함
-운동 집중 및 수분 충전 — 전해질과 아미노산 보충으로 운동 수행 능력 및 집중력 향상에 도움 됨
-찬물 풀림성 우수 — 가루가 물에 쉽게 잘 풀려 운동 중 타서 마시기 편리함</t>
+          <t>상큼하고 부담 없는 맛 — 과일 성분이 블렌딩되어 독한 생강 맛 대신 상큼달콤하게 마시기 좋음
+아침 활력 충전 — 출근길 공복에 섭취 시 몸이 따뜻해지고 졸음이 깨며 활력이 돋음
+귀여운 보틀 디자인 — 미니 보틀 패키지가 아기자기하고 귀여워 챙겨 마시기 즐거움</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 부드러운 육질로 맛있게 단백질 보충 가능함
-한입 크기 편의성 — 닭가슴살볼이 한입 크기로 되어 있어 샐러드나 도시락 곁들임으로 먹기 편함
-간편한 조리법 — 전자레인지에 간단히 데워 양배추 등과 곁들여 먹기 용이함</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 쫄깃하여 식감이 우수함
+다양한 구성과 맛 — 소스통살과 볼 형태의 다양한 구성과 맛으로 질리지 않고 식단 관리 가능함
+간편한 조리 — 전자레인지로 데우기만 하면 되어 식사 대용으로 편리함</t>
         </is>
       </c>
     </row>
@@ -4744,22 +4717,26 @@
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 정가 기준 가격대가 높아 할인 기간에만 구매하게 됨</t>
+          <t>높은 정가 부담 — 품질은 만족스러우나 정가가 비싸 할인 행사 시에만 구매하게 됨</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백의 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 불량 발생 — 선물용으로 동봉된 쇼핑백에 손잡이 끈이 누락되어 배송됨</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>생강 맛 호불호 — 생강 특유의 찡하고 알싸한 맛으로 인해 어린이나 일부 가족에게는 불호가 있음</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>다소 느린 배송 — 주문 후 수령까지 배송 속도가 다소 느리게 느껴짐</t>
+          <t>배송 다소 지연 — 일부 배송 속도가 느리게 느껴졌다는 후기가 있음</t>
         </is>
       </c>
     </row>
@@ -4796,22 +4773,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>29,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5006,7 +4983,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5014,49 +4991,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618639&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260703/B8ckjHxaPLARUlbtHVdP601618639_00_02B8ckjHxaPLARUlbtHVdP.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>1665</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>부담 없는 피로 관리 — 피곤한 날이나 운동 전후 한 포씩 섭취해 활력을 챙기기 좋음</t>
+          <t>휴대 및 섭취 간편 — 낱개 포장 스틱으로 외출이나 여행 시 휴대가 간편하고 물에 타 마시기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>무난하고 괜찮은 맛 — 아르기닌 특유의 거부감 없이 맛이 무난하여 먹기 편함</t>
+          <t>진한 레몬 원액 — 레몬즙 농도가 진하여 아침 음용이나 샐러드 드레싱용으로 활용도가 높음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>체감 효과 미미 — 섭취 후 뚜렷한 신체적 효능이나 변화를 느끼기 어려움</t>
+          <t>다이소 기준 높은 가격 — 다이소 입점 상품 기준으로는 가격대가 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -5065,7 +5042,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5073,49 +5050,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2575</v>
+        <v>737</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 다이소 가격대로 한 달간 간편하게 철분을 보충할 수 있음</t>
+          <t>뛰어난 가성비 — 저렴한 가격에도 비싼 브랜드 제품과 유사한 품질과 맛을 제공함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>어지러움 완화 체감 — 주기적으로 섭취 시 헌혈 철분 수치 개선 및 어지럼증 완화에 도움 됨</t>
+          <t>간편한 섭취 — 스틱 한 포씩 간편하게 짜 먹을 수 있어 일상 피로 완화에 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>효과 체감 부족 — 빈혈 완화 목적으로 섭취했으나 뚜렷한 효과를 체감하지 못함</t>
+          <t>다소 묽은 맛 — 진한 홍삼 농도를 기대한 사람에게는 맛이 다소 싱겁게 느껴짐</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5132,7 +5109,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5142,44 +5119,48 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000283&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/zIbSOpTi3yHSeYULrLdY600000283_00_01zIbSOpTi3yHSeYULrLdY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>283</v>
+        <v>3651</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>높은 가성비 — 저렴한 가격으로 매일 필요한 비타민과 미네랄을 부담 없이 보충함</t>
+          <t>뛰어난 가성비 — 대웅제약 브랜드 제품을 부담 없는 저렴한 가격에 매일 챙길 수 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>소용량 휴대 편의성 — 6일분 소포장 구성으로 여행이나 출장 시 챙겨 다니기 용이함</t>
+          <t>간편한 섭취 — 하루 한 알로 다양한 비타민과 미네랄을 한 번에 보충하기 편리함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>효과 체감 미미 — 단일 고함량 비타민에 비해 복합제 특성상 체감 효과가 크지 않다는 의견 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5187,49 +5168,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3841</v>
+        <v>2835</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 타사 다이어트 보조제 대비 가격이 매우 저렴해 부담 없이 구매 가능함</t>
+          <t>물 대용 음용 편리 — 맹물 마시기 힘들 때 커피 대신 구수하게 타서 마시기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>다이어트 보조 섭취 — 식단 및 체중 관리 시 보조 목적으로 간편하게 복용하기 무난함</t>
+          <t>간편한 휴대와 사용 — 스틱 분말형으로 물에 타 마시기 간편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>체중 감량 체감 부족 — 복용 기간 동안 뚜렷한 다이어트 효과가 나타나지 않아 복용을 중단함</t>
+          <t>평범한 맛 — 커피 대용으로 마시기에는 맛이 평범하고 밋밋하다는 평가가 있음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -5246,58 +5227,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/XgyvZV5zt5ig9XLyfDOS613602129_00_01XgyvZV5zt5ig9XLyfDOS.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>458</v>
+        <v>1181</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>목 칼칼함 완화 — 환절기나 기침, 초기 감기 기운이 있을 때 섭취 시 목이 편안해짐</t>
+          <t>맛있는 구미 젤리 — 달콤한 사과맛 젤리 형태로 아이들도 거부감 없이 간식처럼 잘 먹음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>달콤하고 진한 맛 — 쌍화 특유의 쓴맛이 강하지 않고 배와 도라지의 달콤함이 어우러져 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>간편한 스틱 형태 — 스틱 액상 포장으로 휴대가 간편해 외출 시 바로 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>높은 가성비 — 면역과 프로폴리스를 부담 없는 가격에 챙길 수 있어 가성비가 뛰어남</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>체감 효과 확인 어려움 — 맛있게 먹을 수 있으나 뚜렷한 기능적 체감 효과는 잘 모르겠다는 의견 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5305,12 +5286,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5320,34 +5301,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602146&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260922/duhAbxLjwmJEME9SWJfp613602146_00_01duhAbxLjwmJEME9SWJfp.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1089</v>
+        <v>671</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>작은 캡슐 크기 — 알약 크기가 작아 목넘김이 편하고 섭취 부담이 적음</t>
+          <t>저렴한 가격대 — 가격 부담이 없어 환절기나 피로할 때 가성비로 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>가성비 및 브랜드 신뢰 — 유한양행 제조사 신뢰도가 높고 가격이 착해 부담 없이 섭취 가능함</t>
+          <t>간편한 섭취 — 소용량 병 포장으로 가볍게 복용하기 수월함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>효과 체감의 개인차 — 꾸준히 복용 중이나 장 건강 개선에 대한 체감 효과는 명확하지 않음</t>
+          <t>평범한 효능 체감 — 즉각적인 피로 개선 효과는 크지 않고 무난하다는 평가가 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -5356,7 +5337,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5364,12 +5345,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[여성건강] 종근당 데일리와이즈 리스펙타 유산균 6포 6일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5379,34 +5360,34 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306212&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/LLM8nTqqNcWSJRgwJpaM032306212_00_01LLM8nTqqNcWSJRgwJpaM.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>213</v>
+        <v>1094</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>여성 건강 개선 체감 — 섭취 후 불규칙하던 생리 주기 안정 및 컨디션 관리에 도움 됨</t>
+          <t>음료 대용 섭취 용이 — 물이나 탄산수에 타 마시면 맛있는 음료처럼 즐기며 다이어트 관리가 가능함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>섭취하기 좋은 맛 — 처음엔 낯설 수 있으나 먹다 보면 거부감 없이 맛있게 복용 가능함</t>
+          <t>복용 편의성 — 분말 스틱형으로 간편하게 타서 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>용량 대비 높은 가격 — 6포 단위 소포장으로 다이소 영양제 품목 중에서는 다소 비싸게 느껴짐</t>
+          <t>딸기 감기약맛 호불호 — 인공적인 딸기 물약 맛처럼 느껴져 입맛에 맞지 않는다는 의견 있음</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5415,7 +5396,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5423,66 +5404,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
+          <t>올비텐 멀티비타민 츄어블 30정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>영진약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911098&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/2LpWqYu8CZWzex7rdnk8610911098_00_012LpWqYu8CZWzex7rdnk8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260310/41yPP4FFDsaIkDV2FbEM286314178_00_0141yPP4FFDsaIkDV2FbEM.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 구강 용해 필름 — 물 없이 입안에 가볍게 붙여서 녹여 먹을 수 있어 복용이 간편함</t>
+          <t>어린이 입문용 적합 — 아이들이 거부감 없이 씹어 먹을 수 있는 츄어블 제형임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 향과 맛 — 필름 특유의 향과 맛미가 무난하여 콜라겐과 함께 섭취하기 좋음</t>
+          <t>가성비 대비 충실한 기능 — 저렴한 가격대에 멀티비타민 필수 영양을 채울 수 있음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>아쉬운 복용 맛 — 입안에서 녹을 때의 맛이 기대보다 별로라 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>장당 단가 부담 — 필름 1장당 단가(약 500원)가 다이소 기준 다소 비싸게 느껴져 재구매 망설여짐</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>뚜렷한 효과 미체감 — 피부나 체력 면에서 즉각적인 효능을 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5490,12 +5459,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5505,35 +5474,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>181</v>
+        <v>1776</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>침향의 뛰어난 가성비 — 고가 한방 원료인 침향을 다이소에서 매우 저렴한 가격에 구매 가능함</t>
+          <t>작은 캡슐 크기 — 알약 크기가 작아 목넘김이 편하고 섭취 부담이 없음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 향 — 침향 함량이 과하지 않아 많이 쓰지 않고 진해 부담 없이 씹어 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>활력 및 컨디션 회복 — 하루 한 알 간편하게 섭취해 환절기 피로 개선 및 활력 보충에 도움 됨</t>
-        </is>
-      </c>
+          <t>높은 가성비와 만족도 — 착한 가격에 장 건강 관리 효과를 체감하여 재구매율이 높음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5541,7 +5506,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5549,7 +5514,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5559,44 +5524,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3647</v>
+        <v>2577</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>가성비 높은 종합영양제 — 한 알로 비타민과 미네랄을 저렴한 가격에 매일 챙길 수 있음</t>
+          <t>우수한 가성비 — 다이소 특유의 저렴한 가격으로 간편하게 철분을 보충할 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>위장 부담 완화 — 비타민 복용 시 흔히 발생하는 속 쓰림 현상이 타제품 대비 덜함</t>
+          <t>수치 개선 체감 — 섭취 후 헌혈 검사 시 철분 수치가 상승하는 등의 체감을 느낌</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>단일 성분 대비 미약함 — 멀티 미네랄 제형이라 개별 비타민 단일제 복용 대비 체감 효과가 약함</t>
+          <t>빠른 용해로 인한 약맛 — 입안에서 알약이 빨리 녹아 특유의 약맛이 느껴져 불편함</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>잦은 품절 현상 — 인기 품목이라 재고 품절이 잦아 원하는 시점에 즉시 구매하기 어려움</t>
+          <t>빈혈 체감 효과 미미 — 복용 후 뚜렷한 빈혈 개선 효능을 느끼지 못했다는 의견 있음</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -5712,52 +5677,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -5769,47 +5734,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>영진약품</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>유한양행</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5826,52 +5791,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>올비텐 멀티비타민 츄어블 30정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 철분 30정 30일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[여성건강] 종근당 데일리와이즈 리스펙타 유산균 6포 6일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5847,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5891,10 +5856,10 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.7</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5906,7 +5871,7 @@
         <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5919,37 +5884,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>561</v>
+        <v>1665</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2575</v>
+        <v>737</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>283</v>
+        <v>3651</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3841</v>
+        <v>2835</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>458</v>
+        <v>1181</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1089</v>
+        <v>671</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>213</v>
+        <v>1094</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>181</v>
+        <v>1776</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3647</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5957,68 +5922,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 피로 관리 — 피곤한 날이나 운동 전후 한 포씩 섭취해 활력을 챙기기 좋음
-무난하고 괜찮은 맛 — 아르기닌 특유의 거부감 없이 맛이 무난하여 먹기 편함</t>
+          <t>휴대 및 섭취 간편 — 낱개 포장 스틱으로 외출이나 여행 시 휴대가 간편하고 물에 타 마시기 좋음
+진한 레몬 원액 — 레몬즙 농도가 진하여 아침 음용이나 샐러드 드레싱용으로 활용도가 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 다이소 가격대로 한 달간 간편하게 철분을 보충할 수 있음
-어지러움 완화 체감 — 주기적으로 섭취 시 헌혈 철분 수치 개선 및 어지럼증 완화에 도움 됨</t>
+          <t>뛰어난 가성비 — 저렴한 가격에도 비싼 브랜드 제품과 유사한 품질과 맛을 제공함
+간편한 섭취 — 스틱 한 포씩 간편하게 짜 먹을 수 있어 일상 피로 완화에 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비 — 저렴한 가격으로 매일 필요한 비타민과 미네랄을 부담 없이 보충함
-소용량 휴대 편의성 — 6일분 소포장 구성으로 여행이나 출장 시 챙겨 다니기 용이함</t>
+          <t>뛰어난 가성비 — 대웅제약 브랜드 제품을 부담 없는 저렴한 가격에 매일 챙길 수 있음
+간편한 섭취 — 하루 한 알로 다양한 비타민과 미네랄을 한 번에 보충하기 편리함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 타사 다이어트 보조제 대비 가격이 매우 저렴해 부담 없이 구매 가능함
-다이어트 보조 섭취 — 식단 및 체중 관리 시 보조 목적으로 간편하게 복용하기 무난함</t>
+          <t>물 대용 음용 편리 — 맹물 마시기 힘들 때 커피 대신 구수하게 타서 마시기 좋음
+간편한 휴대와 사용 — 스틱 분말형으로 물에 타 마시기 간편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>목 칼칼함 완화 — 환절기나 기침, 초기 감기 기운이 있을 때 섭취 시 목이 편안해짐
-달콤하고 진한 맛 — 쌍화 특유의 쓴맛이 강하지 않고 배와 도라지의 달콤함이 어우러져 먹기 편함
-간편한 스틱 형태 — 스틱 액상 포장으로 휴대가 간편해 외출 시 바로 챙겨 먹기 좋음</t>
+          <t>맛있는 구미 젤리 — 달콤한 사과맛 젤리 형태로 아이들도 거부감 없이 간식처럼 잘 먹음
+높은 가성비 — 면역과 프로폴리스를 부담 없는 가격에 챙길 수 있어 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>작은 캡슐 크기 — 알약 크기가 작아 목넘김이 편하고 섭취 부담이 적음
-가성비 및 브랜드 신뢰 — 유한양행 제조사 신뢰도가 높고 가격이 착해 부담 없이 섭취 가능함</t>
+          <t>저렴한 가격대 — 가격 부담이 없어 환절기나 피로할 때 가성비로 챙겨 먹기 적합함
+간편한 섭취 — 소용량 병 포장으로 가볍게 복용하기 수월함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>여성 건강 개선 체감 — 섭취 후 불규칙하던 생리 주기 안정 및 컨디션 관리에 도움 됨
-섭취하기 좋은 맛 — 처음엔 낯설 수 있으나 먹다 보면 거부감 없이 맛있게 복용 가능함</t>
+          <t>음료 대용 섭취 용이 — 물이나 탄산수에 타 마시면 맛있는 음료처럼 즐기며 다이어트 관리가 가능함
+복용 편의성 — 분말 스틱형으로 간편하게 타서 섭취하기 편리함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 구강 용해 필름 — 물 없이 입안에 가볍게 붙여서 녹여 먹을 수 있어 복용이 간편함
-부담 없는 향과 맛 — 필름 특유의 향과 맛미가 무난하여 콜라겐과 함께 섭취하기 좋음</t>
+          <t>어린이 입문용 적합 — 아이들이 거부감 없이 씹어 먹을 수 있는 츄어블 제형임
+가성비 대비 충실한 기능 — 저렴한 가격대에 멀티비타민 필수 영양을 채울 수 있음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>침향의 뛰어난 가성비 — 고가 한방 원료인 침향을 다이소에서 매우 저렴한 가격에 구매 가능함
-부담 없는 맛과 향 — 침향 함량이 과하지 않아 많이 쓰지 않고 진해 부담 없이 씹어 먹기 좋음
-활력 및 컨디션 회복 — 하루 한 알 간편하게 섭취해 환절기 피로 개선 및 활력 보충에 도움 됨</t>
+          <t>작은 캡슐 크기 — 알약 크기가 작아 목넘김이 편하고 섭취 부담이 없음
+높은 가성비와 만족도 — 착한 가격에 장 건강 관리 효과를 체감하여 재구매율이 높음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>가성비 높은 종합영양제 — 한 알로 비타민과 미네랄을 저렴한 가격에 매일 챙길 수 있음
-위장 부담 완화 — 비타민 복용 시 흔히 발생하는 속 쓰림 현상이 타제품 대비 덜함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>우수한 가성비 — 다이소 특유의 저렴한 가격으로 간편하게 철분을 보충할 수 있음
+수치 개선 체감 — 섭취 후 헌혈 검사 시 철분 수치가 상승하는 등의 체감을 느낌</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -6026,43 +5989,45 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과 미미 — 섭취 후 뚜렷한 신체적 효능이나 변화를 느끼기 어려움</t>
+          <t>다이소 기준 높은 가격 — 다이소 입점 상품 기준으로는 가격대가 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감 부족 — 빈혈 완화 목적으로 섭취했으나 뚜렷한 효과를 체감하지 못함</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>다소 묽은 맛 — 진한 홍삼 농도를 기대한 사람에게는 맛이 다소 싱겁게 느껴짐</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감 미미 — 단일 고함량 비타민에 비해 복합제 특성상 체감 효과가 크지 않다는 의견 있음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>체중 감량 체감 부족 — 복용 기간 동안 뚜렷한 다이어트 효과가 나타나지 않아 복용을 중단함</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>평범한 맛 — 커피 대용으로 마시기에는 맛이 평범하고 밋밋하다는 평가가 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>체감 효과 확인 어려움 — 맛있게 먹을 수 있으나 뚜렷한 기능적 체감 효과는 잘 모르겠다는 의견 있음</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감의 개인차 — 꾸준히 복용 중이나 장 건강 개선에 대한 체감 효과는 명확하지 않음</t>
+          <t>평범한 효능 체감 — 즉각적인 피로 개선 효과는 크지 않고 무난하다는 평가가 있음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>용량 대비 높은 가격 — 6포 단위 소포장으로 다이소 영양제 품목 중에서는 다소 비싸게 느껴짐</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 복용 맛 — 입안에서 녹을 때의 맛이 기대보다 별로라 호불호가 갈림
-장당 단가 부담 — 필름 1장당 단가(약 500원)가 다이소 기준 다소 비싸게 느껴져 재구매 망설여짐
-뚜렷한 효과 미체감 — 피부나 체력 면에서 즉각적인 효능을 느끼기 어려움</t>
-        </is>
-      </c>
+          <t>딸기 감기약맛 호불호 — 인공적인 딸기 물약 맛처럼 느껴져 입맛에 맞지 않는다는 의견 있음</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>단일 성분 대비 미약함 — 멀티 미네랄 제형이라 개별 비타민 단일제 복용 대비 체감 효과가 약함
-잦은 품절 현상 — 인기 품목이라 재고 품절이 잦아 원하는 시점에 즉시 구매하기 어려움</t>
+          <t>빠른 용해로 인한 약맛 — 입안에서 알약이 빨리 녹아 특유의 약맛이 느껴져 불편함
+빈혈 체감 효과 미미 — 복용 후 뚜렷한 빈혈 개선 효능을 느끼지 못했다는 의견 있음</t>
         </is>
       </c>
     </row>
@@ -6074,52 +6039,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -6306,27 +6271,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[단독기획/10+2] 마그랩 포 스트레스 12입 선물세트 (12일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>마그랩</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>9,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000189370&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018937046ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6376,23 +6341,19 @@
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>이중 기능성 설계 — 장 건강 케어와 체지방 감소를 동시에 관리할 수 있어 다이어트 시 유용함</t>
+          <t>체지방과 장 동시 케어 — 유산균 증식과 체지방 감소 기능성을 동시에 챙길 수 있는 복합 설계임</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>상큼한 요거트 맛 — 비린 맛 없이 상큼한 요거트 맛 분말로 맛있게 하루 한 포 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>속 편안함 체감 — 복용 후 복부 팽만감이 줄어들고 아랫배가 한결 가볍고 편안해짐</t>
-        </is>
-      </c>
+          <t>상큼한 요거트 맛 — 상큼한 요거트 맛 분말로 부담 없이 하루 한 포씩 간편히 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6400,7 +6361,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6408,48 +6369,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>6019</v>
+        <v>25772</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>수면 유도 및 질 개선 — 취침 전 섭취 시 잠드는 시간이 단축되고 아침 기상 시 개운함을 느낌</t>
+          <t>목넘김 편한 초소형 캡슐 — 170mg의 작고 가벼운 캡슐 크기로 목걸림 없이 부드럽게 복용 가능함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>맛있는 포도맛 젤리 — 간식처럼 챙겨 먹기 좋은 맛있는 포도 젤리 제형으로 복용 부담이 없음</t>
+          <t>귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 소장 가치 있는 증정품이 포함됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>식물성 성분 안정성 — 100% 식물성 멜라토닌 추출물로 아침 두통이나 몽롱함 부담이 적음</t>
+          <t>질과 장 더블 케어 — 식약처 인정 원료로 여성 질 건강과 장 건강을 한 번에 관리 가능함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -6459,7 +6420,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6467,37 +6428,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>8467</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1일 1캡슐 간편 복용 — 하루 한 알로 여성 유산균을 간편하게 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>매력적인 굿즈 증정 — 포토카드 및 캐릭터 키링 증정 기획으로 구매 만족도가 높음</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6506,7 +6475,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6514,41 +6483,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>206</v>
+        <v>17324</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>맛있는 이너뷰티 섭취 — 맛없는 분말과 달리 맛이 좋아 간식처럼 거부감 없이 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>붓기 완화 체감 — 야식 섭취나 촬영 전 복용 시 얼굴 부기 제거 및 라인 정리에 도움됨</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>섭취 편한 미니환 — 크기가 작은 미니환 제형이라 물과 함께 목넘김이 수월함</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6557,7 +6530,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6565,27 +6538,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>그래니 살라 VPL정 60정(1개월분)</t>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>그래니샐러드</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22,790원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000253967&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025396704ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294414ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6600,7 +6573,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6608,50 +6581,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>헬시플레이스 더블 토닝 화이트 글루타치온 콜라겐 스틱 14포 (14일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>헬시플레이스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>28,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000233243&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023324308ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>16210</v>
+        <v>1814</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>빠르고 깊은 수면 유도 — 뒤척이던 밤에 섭취 시 잠이 확 들고 숙면을 취하는 데 도움 됨</t>
+          <t>맛있는 청사과맛 젤리 — 상큼달콤하고 쫀득한 젤리 제형으로 간식처럼 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편하고 맛있는 젤리 — 정제 알약이 아닌 맛있는 구미 제형으로 물 없이 자기 전 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>안심 식물성 원료 — 식물성 멜라토닌 성분을 함유하여 부담 없이 안심하고 복용 가능함</t>
-        </is>
-      </c>
+          <t>피부 속광 개선 체감 — 글루타치온과 콜라겐 보충으로 피부가 탱글해지고 메이크업 밀착에 도움됨</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6667,49 +6636,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[단독기획/10+2] 마그랩 포 스트레스 12입 선물세트 (12일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>마그랩</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,500원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000189370&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018937046ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>5512</v>
+        <v>15787</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>새콤달콤한 간식형 젤리 — 상큼한 과일 맛 젤리 형태로 물 없이 언제 어디서나 맛있게 영양 보충 가능함</t>
+          <t>마시는 액상형 편의성 — 알약 없이 마실 수 있는 달콤한 액상형으로 물 없이도 간편히 섭취 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>피로 회복 및 피부 관리 — 지친 퇴근길이나 아침에 활력을 더해주며 피부 관리를 루틴화하기 좋음</t>
+          <t>깔끔한 패키지와 굿즈 — 선물용으로 적합한 패키지 구성 및 귀여운 키링 증정으로 만족스러움</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>섭취 후 양치 번거로움 — 젤리 제형 특성상 밤에 섭취할 경우 양치를 다시 해야 하는 귀찮음이 있음</t>
+          <t>숙면 효과 체감 미미 — 근육 떨림 완화에는 도움되나 숙면 유도 효과는 크게 느끼지 못했다는 의견 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -6718,7 +6687,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6726,48 +6695,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>25764</v>
+        <v>31719</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>질과 장 더블 케어 — 식약처 기능성 원료로 여성 질 건강과 장 건강을 한 알로 케어 가능함</t>
+          <t>배변 활동 개선 체감 — 식후 섭취 시 묵은 변비가 완화되고 화장실을 편하게 가게 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 목넘김이 이물감 없이 수월함</t>
+          <t>휴대 편한 젤리 형태 — 맛있는 젤리 스틱 타입으로 과식 후 간식처럼 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>소장 가치 높은 굿즈 — 포켓몬 에디션 카드케이스 등 귀여운 패키지와 증정품으로 구매 만족도가 높음</t>
+          <t>귀여운 캐릭터 콜라보 — 헬로키티 콜라보 패키지로 귀여움과 소장 가치를 더함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -6777,7 +6746,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6785,39 +6754,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>뉴트리코어 유기농 비타민D 1000IU 2종 중 택1 (2개월분/10개월분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>뉴트리코어</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43,230원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000203546&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020354605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>27092</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>체지방 관리 도움 — 식단 관리가 어려울 때 체지방 관리와 붓기 완화 루틴으로 챙기기 적합함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>귀여운 패키지 디자인 — 헬로키티 콜라보 등 감각적인 디자인으로 챙겨 먹는 재미가 있음</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 정제 크기가 다소 커서 삼킬 때 목넘김에 부담을 느낄 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6942,42 +6923,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6989,52 +6970,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>헬시플레이스</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>마그랩</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>그래니샐러드</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>뉴트리코어</t>
+          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -7046,52 +7027,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>헬시플레이스 더블 토닝 화이트 글루타치온 콜라겐 스틱 14포 (14일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[단독기획/10+2] 마그랩 포 스트레스 12입 선물세트 (12일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>그래니 살라 VPL정 60정(1개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>뉴트리코어 유기농 비타민D 1000IU 2종 중 택1 (2개월분/10개월분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
     </row>
@@ -7106,26 +7087,26 @@
         <v>4.5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -7136,29 +7117,29 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6019</v>
+        <v>25772</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>319</v>
+        <v>8467</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>206</v>
+        <v>17324</v>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="n">
-        <v>16210</v>
+        <v>1814</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5512</v>
+        <v>15787</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>25764</v>
+        <v>31719</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>17</v>
+        <v>27092</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7170,46 +7151,55 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>이중 기능성 설계 — 장 건강 케어와 체지방 감소를 동시에 관리할 수 있어 다이어트 시 유용함
-상큼한 요거트 맛 — 비린 맛 없이 상큼한 요거트 맛 분말로 맛있게 하루 한 포 섭취 가능함
-속 편안함 체감 — 복용 후 복부 팽만감이 줄어들고 아랫배가 한결 가볍고 편안해짐</t>
+          <t>체지방과 장 동시 케어 — 유산균 증식과 체지방 감소 기능성을 동시에 챙길 수 있는 복합 설계임
+상큼한 요거트 맛 — 상큼한 요거트 맛 분말로 부담 없이 하루 한 포씩 간편히 섭취 가능함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>수면 유도 및 질 개선 — 취침 전 섭취 시 잠드는 시간이 단축되고 아침 기상 시 개운함을 느낌
-맛있는 포도맛 젤리 — 간식처럼 챙겨 먹기 좋은 맛있는 포도 젤리 제형으로 복용 부담이 없음
-식물성 성분 안정성 — 100% 식물성 멜라토닌 추출물로 아침 두통이나 몽롱함 부담이 적음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>목넘김 편한 초소형 캡슐 — 170mg의 작고 가벼운 캡슐 크기로 목걸림 없이 부드럽게 복용 가능함
+귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 소장 가치 있는 증정품이 포함됨
+질과 장 더블 케어 — 식약처 인정 원료로 여성 질 건강과 장 건강을 한 번에 관리 가능함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1일 1캡슐 간편 복용 — 하루 한 알로 여성 유산균을 간편하게 챙길 수 있음
+매력적인 굿즈 증정 — 포토카드 및 캐릭터 키링 증정 기획으로 구매 만족도가 높음</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 이너뷰티 섭취 — 맛없는 분말과 달리 맛이 좋아 간식처럼 거부감 없이 챙겨 먹기 적합함</t>
+          <t>붓기 완화 체감 — 야식 섭취나 촬영 전 복용 시 얼굴 부기 제거 및 라인 정리에 도움됨
+섭취 편한 미니환 — 크기가 작은 미니환 제형이라 물과 함께 목넘김이 수월함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>빠르고 깊은 수면 유도 — 뒤척이던 밤에 섭취 시 잠이 확 들고 숙면을 취하는 데 도움 됨
-간편하고 맛있는 젤리 — 정제 알약이 아닌 맛있는 구미 제형으로 물 없이 자기 전 챙겨 먹기 편함
-안심 식물성 원료 — 식물성 멜라토닌 성분을 함유하여 부담 없이 안심하고 복용 가능함</t>
+          <t>맛있는 청사과맛 젤리 — 상큼달콤하고 쫀득한 젤리 제형으로 간식처럼 맛있게 섭취 가능함
+피부 속광 개선 체감 — 글루타치온과 콜라겐 보충으로 피부가 탱글해지고 메이크업 밀착에 도움됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>새콤달콤한 간식형 젤리 — 상큼한 과일 맛 젤리 형태로 물 없이 언제 어디서나 맛있게 영양 보충 가능함
-피로 회복 및 피부 관리 — 지친 퇴근길이나 아침에 활력을 더해주며 피부 관리를 루틴화하기 좋음</t>
+          <t>마시는 액상형 편의성 — 알약 없이 마실 수 있는 달콤한 액상형으로 물 없이도 간편히 섭취 가능함
+깔끔한 패키지와 굿즈 — 선물용으로 적합한 패키지 구성 및 귀여운 키링 증정으로 만족스러움</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>질과 장 더블 케어 — 식약처 기능성 원료로 여성 질 건강과 장 건강을 한 알로 케어 가능함
-초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 목넘김이 이물감 없이 수월함
-소장 가치 높은 굿즈 — 포켓몬 에디션 카드케이스 등 귀여운 패키지와 증정품으로 구매 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>배변 활동 개선 체감 — 식후 섭취 시 묵은 변비가 완화되고 화장실을 편하게 가게 됨
+휴대 편한 젤리 형태 — 맛있는 젤리 스틱 타입으로 과식 후 간식처럼 챙겨 먹기 용이함
+귀여운 캐릭터 콜라보 — 헬로키티 콜라보 패키지로 귀여움과 소장 가치를 더함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>체지방 관리 도움 — 식단 관리가 어려울 때 체지방 관리와 붓기 완화 루틴으로 챙기기 적합함
+귀여운 패키지 디자인 — 헬로키티 콜라보 등 감각적인 디자인으로 챙겨 먹는 재미가 있음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7226,11 +7216,15 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>섭취 후 양치 번거로움 — 젤리 제형 특성상 밤에 섭취할 경우 양치를 다시 해야 하는 귀찮음이 있음</t>
+          <t>숙면 효과 체감 미미 — 근육 떨림 완화에는 도움되나 숙면 유도 효과는 크게 느끼지 못했다는 의견 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 정제 크기가 다소 커서 삼킬 때 목넘김에 부담을 느낄 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7240,52 +7234,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>28,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>20,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>22,790원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>9,500원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>43,230원</t>
+          <t>17,900원</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7415,19 +7409,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7437,13 +7431,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -7459,25 +7453,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7487,10 +7481,10 @@
         <v>7.5</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -7499,36 +7493,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -7537,13 +7531,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7560,50 +7554,6 @@
       </c>
       <c r="F8" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
